--- a/docs/verification/files/rocscience_gw/gw016a.xlsx
+++ b/docs/verification/files/rocscience_gw/gw016a.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="266">
   <si>
     <t>X</t>
   </si>
@@ -1023,6 +1023,9 @@
   </si>
   <si>
     <t>save_times</t>
+  </si>
+  <si>
+    <t>reservoir</t>
   </si>
 </sst>
 </file>
@@ -13819,7 +13822,9 @@
       <c r="O6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-      <c r="T6" s="1"/>
+      <c r="T6" s="1" t="s">
+        <v>265</v>
+      </c>
       <c r="U6" s="9"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
@@ -14085,7 +14090,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 H3 K3 N3 Q3" xr:uid="{21F200C9-4829-4345-9958-0F754F272AD0}">
-      <formula1>$T$4:$T$5</formula1>
+      <formula1>$T$4:$T$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14235,6 +14240,9 @@
       <c r="O6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
+      <c r="T6" s="1" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
@@ -14499,7 +14507,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 H3 K3 N3 Q3" xr:uid="{68C61D93-1721-F843-8E53-0F0E50006C65}">
-      <formula1>$T$4:$T$5</formula1>
+      <formula1>$T$4:$T$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/verification/files/rocscience_gw/gw016a.xlsx
+++ b/docs/verification/files/rocscience_gw/gw016a.xlsx
@@ -14240,9 +14240,6 @@
       <c r="O6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-      <c r="T6" s="1" t="s">
-        <v>265</v>
-      </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
@@ -14507,7 +14504,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 H3 K3 N3 Q3" xr:uid="{68C61D93-1721-F843-8E53-0F0E50006C65}">
-      <formula1>$T$4:$T$6</formula1>
+      <formula1>$T$4:$T$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15829,10 +15826,10 @@
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3">
-        <v>100000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N11" s="3">
-        <v>0.3</v>
+        <v>0.0</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>

--- a/docs/verification/files/rocscience_gw/gw016a.xlsx
+++ b/docs/verification/files/rocscience_gw/gw016a.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C0E255-0472-174F-97B1-AC3DD61E05E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523500CF-89B8-4644-B955-31C74218CF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18260" yWindow="3440" windowWidth="44060" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="4320" windowWidth="46940" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="318">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -875,9 +875,6 @@
   </si>
   <si>
     <t>I</t>
-  </si>
-  <si>
-    <t>Fixity</t>
   </si>
   <si>
     <t>P</t>
@@ -1116,6 +1113,27 @@
   </si>
   <si>
     <t>yr</t>
+  </si>
+  <si>
+    <t>Adhesion</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>1D element size:</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>Tip</t>
+  </si>
+  <si>
+    <t>Pinned</t>
+  </si>
+  <si>
+    <t>Unrotated</t>
   </si>
 </sst>
 </file>
@@ -1886,16 +1904,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>217714</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>54430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>199571</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>9071</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>90714</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1910,8 +1928,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14804571" y="254001"/>
-          <a:ext cx="3610429" cy="3746499"/>
+          <a:off x="16455571" y="254001"/>
+          <a:ext cx="3855358" cy="4027713"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2035,6 +2053,31 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Adhesion</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = soii-reinforcement interface adhesion (blank</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = use Lp)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>Delta</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = soil-reinforcement interface friction angle (blank = use Lp)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Tend1, Tend2 </a:t>
           </a:r>
           <a:r>
@@ -2081,6 +2124,10 @@
             <a:rPr lang="en-US" sz="1100" b="0"/>
             <a:t> = cross-sectional area of reinforcement (FEM only)</a:t>
           </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2093,16 +2140,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>308429</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>290286</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:rowOff>126999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>571501</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>145143</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>553358</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2117,8 +2164,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13398500" y="190499"/>
-          <a:ext cx="3156858" cy="2349501"/>
+          <a:off x="14205857" y="126999"/>
+          <a:ext cx="3156858" cy="2521858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2423,7 +2470,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Fixity</a:t>
+            <a:t>Head</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
@@ -2435,8 +2482,54 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> = Pile head status (fixed or free)</a:t>
+            <a:t> = Pile head fixity status</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tip</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile tip fixity status</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -2788,7 +2881,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="30">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -2964,7 +3057,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C20" s="14" t="s">
-        <v>45</v>
+        <v>313</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>46</v>
@@ -2976,7 +3069,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C21" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>49</v>
@@ -2988,28 +3081,34 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="1"/>
+        <v>48</v>
+      </c>
       <c r="F22" s="1"/>
+      <c r="D22"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
       <c r="C23" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="1"/>
-      <c r="C24" s="14" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D24"/>
+      <c r="D25"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="s">
@@ -3053,7 +3152,7 @@
     </row>
     <row r="58" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D58" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
@@ -3151,7 +3250,7 @@
     <mergeCell ref="B7:D7"/>
   </mergeCells>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"rollers,fixed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -3169,10 +3268,10 @@
     <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>$D$75:$D$79</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"auto,manual"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D25" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"circular,non-circular"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3182,18 +3281,18 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A2:AB25"/>
+  <dimension ref="A2:AD25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="6" width="10.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" customWidth="1"/>
-    <col min="10" max="12" width="10.83203125" style="1" customWidth="1"/>
-    <col min="16" max="18" width="10.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="4.33203125" customWidth="1"/>
+    <col min="10" max="14" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="20" width="10.83203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>194</v>
       </c>
@@ -3231,34 +3330,40 @@
         <v>252</v>
       </c>
       <c r="M2" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="O2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="R2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="Q2" s="28" t="s">
+      <c r="S2" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="R2" s="28" t="s">
+      <c r="T2" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>258</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>259</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3269,11 +3374,11 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="str">
-        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,2,0),""))</f>
+        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,3,0),""))</f>
+        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J3" s="3"/>
@@ -3285,17 +3390,19 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
-      <c r="Z3" t="s">
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="AB3" t="s">
         <v>261</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AC3" t="s">
         <v>262</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AD3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -3322,11 +3429,13 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
-      <c r="Z4" t="s">
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="AB4" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -3353,11 +3462,13 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-      <c r="Z5" t="s">
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="AB5" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -3384,8 +3495,10 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -3412,8 +3525,10 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -3440,17 +3555,19 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-      <c r="Z8" t="s">
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="AB8" t="s">
         <v>258</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AC8" t="s">
         <v>259</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AD8" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -3477,17 +3594,19 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="Z9" t="s">
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="AB9" t="s">
         <v>261</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AC9" t="s">
         <v>262</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AD9" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -3514,17 +3633,19 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="Z10" t="s">
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="AB10" t="s">
         <v>264</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="AC10" t="s">
         <v>262</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AD10" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -3551,17 +3672,19 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="Z11" t="s">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="AB11" t="s">
         <v>265</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AC11" t="s">
         <v>262</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AD11" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -3588,8 +3711,10 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -3616,8 +3741,10 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -3644,8 +3771,10 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -3672,8 +3801,10 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -3700,8 +3831,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -3728,8 +3861,10 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -3756,8 +3891,10 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -3784,8 +3921,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -3812,8 +3951,10 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -3840,8 +3981,10 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -3868,39 +4011,41 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="T23" s="42"/>
-      <c r="U23" t="s">
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V23" s="42"/>
+      <c r="W23" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="9" t="s">
+      <c r="V24" s="26"/>
+      <c r="W24" s="9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="9" t="s">
+      <c r="V25" s="29"/>
+      <c r="W25" s="9" t="s">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G22" xr:uid="{00000000-0002-0000-0900-000000000000}">
-      <formula1>$Z$2:$Z$5</formula1>
+      <formula1>$AB$2:$AB$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H22" xr:uid="{00000000-0002-0000-0900-000001000000}">
-      <formula1>$AA$2:$AA$3</formula1>
+      <formula1>$AC$2:$AC$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I22" xr:uid="{00000000-0002-0000-0900-000002000000}">
-      <formula1>$AB$2:$AB$3</formula1>
+      <formula1>$AD$2:$AD$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3910,18 +4055,18 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A2:Z17"/>
+  <dimension ref="A2:AA17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
     <col min="3" max="7" width="10.83203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" customWidth="1"/>
-    <col min="9" max="16" width="10.83203125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="5.5" customWidth="1"/>
+    <col min="9" max="17" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>194</v>
       </c>
@@ -3968,16 +4113,19 @@
         <v>257</v>
       </c>
       <c r="P2" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="Y2" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>315</v>
+      </c>
+      <c r="Z2" t="s">
         <v>222</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3996,14 +4144,15 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
-      <c r="Y3" t="s">
-        <v>226</v>
-      </c>
+      <c r="Q3" s="3"/>
       <c r="Z3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AA3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -4022,8 +4171,12 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q4" s="3"/>
+      <c r="Z4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -4042,8 +4195,12 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q5" s="3"/>
+      <c r="Z5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -4062,8 +4219,9 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -4082,8 +4240,9 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -4102,8 +4261,9 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -4122,8 +4282,9 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -4142,8 +4303,9 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -4162,8 +4324,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -4182,36 +4345,37 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R15" s="42"/>
-      <c r="S15" t="s">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S15" s="42"/>
+      <c r="T15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R16" s="26"/>
-      <c r="S16" s="9" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S16" s="26"/>
+      <c r="T16" s="9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="18:19" x14ac:dyDescent="0.2">
-      <c r="R17" s="29"/>
-      <c r="S17" s="9" t="s">
+    <row r="17" spans="19:20" x14ac:dyDescent="0.2">
+      <c r="S17" s="29"/>
+      <c r="T17" s="9" t="s">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
-      <formula1>$Y$2:$Y$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
+      <formula1>$AA$2:$AA$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
-      <formula1>$Z$2:$Z$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>$Z$2:$Z$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4243,10 +4407,10 @@
         <v>167</v>
       </c>
       <c r="E2" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>273</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -4469,27 +4633,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="59" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="59" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="59" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="59" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4507,23 +4671,23 @@
         </is>
       </c>
       <c r="H3" s="32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I3" s="33"/>
       <c r="K3" s="32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
@@ -4564,10 +4728,10 @@
         <v>167</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="U4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4588,10 +4752,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="U5" t="s">
         <v>284</v>
-      </c>
-      <c r="U5" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4612,7 +4776,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -4901,27 +5065,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="60" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="60" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="60" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="60" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4929,27 +5093,27 @@
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F3" s="35"/>
       <c r="H3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I3" s="35"/>
       <c r="K3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
@@ -4990,10 +5154,10 @@
         <v>167</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="U4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -5010,10 +5174,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="U5" t="s">
         <v>284</v>
-      </c>
-      <c r="U5" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -5322,16 +5486,16 @@
         </is>
       </c>
       <c r="D2" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="E2" s="50" t="s">
         <v>295</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="F2" s="50" t="s">
         <v>296</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="G2" s="50" t="s">
         <v>297</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -5346,7 +5510,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J3" s="3">
         <v>0.5005</v>
@@ -5374,7 +5538,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -5396,7 +5560,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -5408,7 +5572,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -5420,7 +5584,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -6443,7 +6607,7 @@
         <v>113</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E10" s="44" t="s">
         <v>114</v>
@@ -6512,22 +6676,22 @@
         <v>134</v>
       </c>
       <c r="AA10" s="46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AB10" s="46" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AC10" s="47" t="s">
         <v>135</v>
       </c>
       <c r="AD10" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="AE10" s="46" t="s">
         <v>307</v>
       </c>
-      <c r="AE10" s="46" t="s">
+      <c r="AF10" s="47" t="s">
         <v>308</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>309</v>
       </c>
       <c r="AG10" s="23" t="s">
         <v>136</v>
@@ -10777,6 +10941,7 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="S4:T4"/>
     <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH4:AI4"/>
@@ -10806,7 +10971,6 @@
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="S4:T4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">
@@ -11147,7 +11311,7 @@
         <v>0.25</v>
       </c>
       <c r="C3" s="3">
-        <v>2.0</v>
+        <v>1.0583333333</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -11155,7 +11319,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>0.0</v>
+        <v>0.85</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -11549,7 +11713,7 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
@@ -12098,7 +12262,7 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
